--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1629,6 +1629,324 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121659103</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>750865</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7135826</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121659101</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>750896</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7136026</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121659096</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>750985</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7136054</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659101</v>
+        <v>121659096</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750896</v>
+        <v>750985</v>
       </c>
       <c r="R10" t="n">
-        <v>7136026</v>
+        <v>7136054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659103</v>
+        <v>121659101</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,27 +1754,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1782,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750865</v>
+        <v>750896</v>
       </c>
       <c r="R11" t="n">
-        <v>7135826</v>
+        <v>7136026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,6 +1825,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121659096</v>
+        <v>121659103</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,26 +1860,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1887,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750985</v>
+        <v>750865</v>
       </c>
       <c r="R12" t="n">
-        <v>7136054</v>
+        <v>7135826</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,7 +1932,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659101</v>
+        <v>121659103</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,26 +1754,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1781,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750896</v>
+        <v>750865</v>
       </c>
       <c r="R11" t="n">
-        <v>7136026</v>
+        <v>7135826</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1826,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121659103</v>
+        <v>121659101</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,27 +1860,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1888,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750865</v>
+        <v>750896</v>
       </c>
       <c r="R12" t="n">
-        <v>7135826</v>
+        <v>7136026</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,6 +1931,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659096</v>
+        <v>121659101</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750985</v>
+        <v>750896</v>
       </c>
       <c r="R10" t="n">
-        <v>7136054</v>
+        <v>7136026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659103</v>
+        <v>121659096</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,27 +1754,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1782,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750865</v>
+        <v>750985</v>
       </c>
       <c r="R11" t="n">
-        <v>7135826</v>
+        <v>7136054</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,6 +1825,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121659101</v>
+        <v>121659103</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,26 +1860,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1887,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750896</v>
+        <v>750865</v>
       </c>
       <c r="R12" t="n">
-        <v>7136026</v>
+        <v>7135826</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,7 +1932,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1632,7 +1632,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659101</v>
+        <v>121659096</v>
       </c>
       <c r="B10" t="n">
         <v>78616</v>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750896</v>
+        <v>750985</v>
       </c>
       <c r="R10" t="n">
-        <v>7136026</v>
+        <v>7136054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659096</v>
+        <v>121659103</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,26 +1754,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1781,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750985</v>
+        <v>750865</v>
       </c>
       <c r="R11" t="n">
-        <v>7136054</v>
+        <v>7135826</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1826,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121659103</v>
+        <v>121659101</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,27 +1860,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1888,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750865</v>
+        <v>750896</v>
       </c>
       <c r="R12" t="n">
-        <v>7135826</v>
+        <v>7136026</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,6 +1931,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659096</v>
+        <v>121659101</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750985</v>
+        <v>750896</v>
       </c>
       <c r="R10" t="n">
-        <v>7136054</v>
+        <v>7136026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1741,7 +1741,7 @@
         <v>121659103</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121659101</v>
+        <v>121659096</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750896</v>
+        <v>750985</v>
       </c>
       <c r="R12" t="n">
-        <v>7136026</v>
+        <v>7136054</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659101</v>
+        <v>121659103</v>
       </c>
       <c r="B10" t="n">
-        <v>78629</v>
+        <v>57381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,26 +1648,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1675,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750896</v>
+        <v>750865</v>
       </c>
       <c r="R10" t="n">
-        <v>7136026</v>
+        <v>7135826</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,7 +1720,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659103</v>
+        <v>121659101</v>
       </c>
       <c r="B11" t="n">
-        <v>57381</v>
+        <v>78631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,27 +1754,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1782,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750865</v>
+        <v>750896</v>
       </c>
       <c r="R11" t="n">
-        <v>7135826</v>
+        <v>7136026</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,6 +1825,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>121659096</v>
       </c>
       <c r="B12" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1741,7 +1741,7 @@
         <v>121659101</v>
       </c>
       <c r="B11" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>121659096</v>
       </c>
       <c r="B12" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1948,6 +1948,758 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125232702</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>750862</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7135880</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125232522</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>750844</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7136020</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125232631</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>750805</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7135996</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125232436</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>750987</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7136030</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125232601</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>750822</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7135979</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125232751</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96979</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>750869</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7135811</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125232490</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Högliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>750909</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7136045</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232702</v>
+        <v>125232751</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,31 +1966,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1998,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750862</v>
+        <v>750869</v>
       </c>
       <c r="R13" t="n">
-        <v>7135880</v>
+        <v>7135811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,6 +2038,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2060,7 +2057,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125232522</v>
+        <v>125232631</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2104,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750844</v>
+        <v>750805</v>
       </c>
       <c r="R14" t="n">
-        <v>7136020</v>
+        <v>7135996</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2164,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125232631</v>
+        <v>125232522</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2211,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750805</v>
+        <v>750844</v>
       </c>
       <c r="R15" t="n">
-        <v>7135996</v>
+        <v>7136020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,7 +2271,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125232436</v>
+        <v>125232601</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2318,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750987</v>
+        <v>750822</v>
       </c>
       <c r="R16" t="n">
-        <v>7136030</v>
+        <v>7135979</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232601</v>
+        <v>125232436</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2425,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750822</v>
+        <v>750987</v>
       </c>
       <c r="R17" t="n">
-        <v>7135979</v>
+        <v>7136030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,10 +2485,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232751</v>
+        <v>125232702</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,27 +2501,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2532,10 +2533,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750869</v>
+        <v>750862</v>
       </c>
       <c r="R18" t="n">
-        <v>7135811</v>
+        <v>7135880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2577,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232751</v>
+        <v>125232601</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,25 +1962,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750869</v>
+        <v>750822</v>
       </c>
       <c r="R13" t="n">
-        <v>7135811</v>
+        <v>7135979</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125232631</v>
+        <v>125232490</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750805</v>
+        <v>750909</v>
       </c>
       <c r="R14" t="n">
-        <v>7135996</v>
+        <v>7136045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2271,7 +2271,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125232601</v>
+        <v>125232436</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750822</v>
+        <v>750987</v>
       </c>
       <c r="R16" t="n">
-        <v>7135979</v>
+        <v>7136030</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232436</v>
+        <v>125232702</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,31 +2390,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2422,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750987</v>
+        <v>750862</v>
       </c>
       <c r="R17" t="n">
-        <v>7136030</v>
+        <v>7135880</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,7 +2470,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2485,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232702</v>
+        <v>125232631</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2497,35 +2500,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2533,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750862</v>
+        <v>750805</v>
       </c>
       <c r="R18" t="n">
-        <v>7135880</v>
+        <v>7135996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,6 +2576,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125232490</v>
+        <v>125232751</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,25 +2607,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750909</v>
+        <v>750869</v>
       </c>
       <c r="R19" t="n">
-        <v>7136045</v>
+        <v>7135811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1950,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232601</v>
+        <v>125232522</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750822</v>
+        <v>750844</v>
       </c>
       <c r="R13" t="n">
-        <v>7135979</v>
+        <v>7136020</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125232490</v>
+        <v>125232702</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,31 +2069,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2101,10 +2105,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750909</v>
+        <v>750862</v>
       </c>
       <c r="R14" t="n">
-        <v>7136045</v>
+        <v>7135880</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2149,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2164,7 +2167,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125232522</v>
+        <v>125232601</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2208,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750844</v>
+        <v>750822</v>
       </c>
       <c r="R15" t="n">
-        <v>7136020</v>
+        <v>7135979</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125232436</v>
+        <v>125232751</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,25 +2286,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2315,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750987</v>
+        <v>750869</v>
       </c>
       <c r="R16" t="n">
-        <v>7136030</v>
+        <v>7135811</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232702</v>
+        <v>125232490</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,35 +2393,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750862</v>
+        <v>750909</v>
       </c>
       <c r="R17" t="n">
-        <v>7135880</v>
+        <v>7136045</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,6 +2469,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125232751</v>
+        <v>125232436</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,25 +2607,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750869</v>
+        <v>750987</v>
       </c>
       <c r="R19" t="n">
-        <v>7135811</v>
+        <v>7136030</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2700,6 +2700,108 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125382120</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västermark, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>751035</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7136038</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1950,7 +1950,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232522</v>
+        <v>125232631</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750844</v>
+        <v>750805</v>
       </c>
       <c r="R13" t="n">
-        <v>7136020</v>
+        <v>7135996</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125232601</v>
+        <v>125232522</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750822</v>
+        <v>750844</v>
       </c>
       <c r="R15" t="n">
-        <v>7135979</v>
+        <v>7136020</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125232751</v>
+        <v>125232601</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,25 +2286,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750869</v>
+        <v>750822</v>
       </c>
       <c r="R16" t="n">
-        <v>7135811</v>
+        <v>7135979</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232490</v>
+        <v>125232751</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,25 +2393,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750909</v>
+        <v>750869</v>
       </c>
       <c r="R17" t="n">
-        <v>7136045</v>
+        <v>7135811</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232631</v>
+        <v>125232436</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750805</v>
+        <v>750987</v>
       </c>
       <c r="R18" t="n">
-        <v>7135996</v>
+        <v>7136030</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125232436</v>
+        <v>125232490</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750987</v>
+        <v>750909</v>
       </c>
       <c r="R19" t="n">
-        <v>7136030</v>
+        <v>7136045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232631</v>
+        <v>125232751</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,25 +1962,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750805</v>
+        <v>750869</v>
       </c>
       <c r="R13" t="n">
-        <v>7135996</v>
+        <v>7135811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125232702</v>
+        <v>125232631</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,35 +2069,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2105,10 +2101,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750862</v>
+        <v>750805</v>
       </c>
       <c r="R14" t="n">
-        <v>7135880</v>
+        <v>7135996</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2149,6 +2145,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2381,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232751</v>
+        <v>125232490</v>
       </c>
       <c r="B17" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2393,25 +2390,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2425,10 +2422,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750869</v>
+        <v>750909</v>
       </c>
       <c r="R17" t="n">
-        <v>7135811</v>
+        <v>7136045</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2595,10 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125232490</v>
+        <v>125232702</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,31 +2604,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2639,10 +2640,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750909</v>
+        <v>750862</v>
       </c>
       <c r="R19" t="n">
-        <v>7136045</v>
+        <v>7135880</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,7 +2684,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>125232751</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>97147</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>125232631</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125232522</v>
+        <v>125232490</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750844</v>
+        <v>750909</v>
       </c>
       <c r="R15" t="n">
-        <v>7136020</v>
+        <v>7136045</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125232601</v>
+        <v>125232702</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,31 +2283,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2315,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750822</v>
+        <v>750862</v>
       </c>
       <c r="R16" t="n">
-        <v>7135979</v>
+        <v>7135880</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2363,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2378,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232490</v>
+        <v>125232436</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750909</v>
+        <v>750987</v>
       </c>
       <c r="R17" t="n">
-        <v>7136045</v>
+        <v>7136030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232436</v>
+        <v>125232522</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750987</v>
+        <v>750844</v>
       </c>
       <c r="R18" t="n">
-        <v>7136030</v>
+        <v>7136020</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125232702</v>
+        <v>125232601</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,35 +2607,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2640,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750862</v>
+        <v>750822</v>
       </c>
       <c r="R19" t="n">
-        <v>7135880</v>
+        <v>7135979</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,6 +2683,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>125382120</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1950,10 +1950,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232751</v>
+        <v>125232702</v>
       </c>
       <c r="B13" t="n">
-        <v>97147</v>
+        <v>56836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,27 +1966,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1994,10 +1998,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750869</v>
+        <v>750862</v>
       </c>
       <c r="R13" t="n">
-        <v>7135811</v>
+        <v>7135880</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,7 +2042,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2057,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125232631</v>
+        <v>125232751</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
+        <v>97147</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,25 +2072,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750805</v>
+        <v>750869</v>
       </c>
       <c r="R14" t="n">
-        <v>7135996</v>
+        <v>7135811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,7 +2167,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125232490</v>
+        <v>125232601</v>
       </c>
       <c r="B15" t="n">
         <v>98269</v>
@@ -2208,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750909</v>
+        <v>750822</v>
       </c>
       <c r="R15" t="n">
-        <v>7136045</v>
+        <v>7135979</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125232702</v>
+        <v>125232522</v>
       </c>
       <c r="B16" t="n">
-        <v>56836</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,35 +2286,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2319,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750862</v>
+        <v>750844</v>
       </c>
       <c r="R16" t="n">
-        <v>7135880</v>
+        <v>7136020</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,6 +2362,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232436</v>
+        <v>125232490</v>
       </c>
       <c r="B17" t="n">
         <v>98269</v>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750987</v>
+        <v>750909</v>
       </c>
       <c r="R17" t="n">
-        <v>7136030</v>
+        <v>7136045</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232522</v>
+        <v>125232631</v>
       </c>
       <c r="B18" t="n">
         <v>98269</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750844</v>
+        <v>750805</v>
       </c>
       <c r="R18" t="n">
-        <v>7136020</v>
+        <v>7135996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125232601</v>
+        <v>125232436</v>
       </c>
       <c r="B19" t="n">
         <v>98269</v>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750822</v>
+        <v>750987</v>
       </c>
       <c r="R19" t="n">
-        <v>7135979</v>
+        <v>7136030</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1950,47 +1950,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232702</v>
+        <v>125232522</v>
       </c>
       <c r="B13" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1998,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750862</v>
+        <v>750844</v>
       </c>
       <c r="R13" t="n">
-        <v>7135880</v>
+        <v>7136020</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,6 +2033,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2060,37 +2052,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125232751</v>
+        <v>125232631</v>
       </c>
       <c r="B14" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750869</v>
+        <v>750805</v>
       </c>
       <c r="R14" t="n">
-        <v>7135811</v>
+        <v>7135996</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,15 +2154,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125232601</v>
+        <v>125232436</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750822</v>
+        <v>750987</v>
       </c>
       <c r="R15" t="n">
-        <v>7135979</v>
+        <v>7136030</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,15 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125232522</v>
+        <v>125232490</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750844</v>
+        <v>750909</v>
       </c>
       <c r="R16" t="n">
-        <v>7136020</v>
+        <v>7136045</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,15 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232490</v>
+        <v>125232601</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750909</v>
+        <v>750822</v>
       </c>
       <c r="R17" t="n">
-        <v>7136045</v>
+        <v>7135979</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,43 +2460,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232631</v>
+        <v>125232702</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2532,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750805</v>
+        <v>750862</v>
       </c>
       <c r="R18" t="n">
-        <v>7135996</v>
+        <v>7135880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2547,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2595,37 +2565,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125232436</v>
+        <v>125232751</v>
       </c>
       <c r="B19" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750987</v>
+        <v>750869</v>
       </c>
       <c r="R19" t="n">
-        <v>7136030</v>
+        <v>7135811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,12 +2670,7 @@
         <v>125382120</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>125232522</v>
       </c>
       <c r="B13" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>125232631</v>
       </c>
       <c r="B14" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>125232436</v>
       </c>
       <c r="B15" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>125232490</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,38 +2358,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232601</v>
+        <v>125232702</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>56843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2397,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750822</v>
+        <v>750862</v>
       </c>
       <c r="R17" t="n">
-        <v>7135979</v>
+        <v>7135880</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,7 +2445,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2460,42 +2463,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232702</v>
+        <v>125232601</v>
       </c>
       <c r="B18" t="n">
-        <v>56843</v>
+        <v>98331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2503,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750862</v>
+        <v>750822</v>
       </c>
       <c r="R18" t="n">
-        <v>7135880</v>
+        <v>7135979</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2547,6 +2546,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>125232751</v>
       </c>
       <c r="B19" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2358,42 +2358,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232702</v>
+        <v>125232601</v>
       </c>
       <c r="B17" t="n">
-        <v>56843</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2401,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750862</v>
+        <v>750822</v>
       </c>
       <c r="R17" t="n">
-        <v>7135880</v>
+        <v>7135979</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2445,6 +2441,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2463,38 +2460,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232601</v>
+        <v>125232702</v>
       </c>
       <c r="B18" t="n">
-        <v>98331</v>
+        <v>56843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2502,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750822</v>
+        <v>750862</v>
       </c>
       <c r="R18" t="n">
-        <v>7135979</v>
+        <v>7135880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,7 +2547,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2670,7 +2670,7 @@
         <v>125382120</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2670,7 +2670,7 @@
         <v>125382120</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2767,7 +2767,7 @@
         <v>129617314</v>
       </c>
       <c r="B21" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2880,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129617666</v>
+        <v>129616393</v>
       </c>
       <c r="B22" t="n">
-        <v>91581</v>
+        <v>82910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Råkälen, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750935</v>
+        <v>750947</v>
       </c>
       <c r="R22" t="n">
-        <v>7135758</v>
+        <v>7135699</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129616393</v>
+        <v>129617666</v>
       </c>
       <c r="B23" t="n">
-        <v>82905</v>
+        <v>91587</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,34 +2988,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råkälen, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750947</v>
+        <v>750935</v>
       </c>
       <c r="R23" t="n">
-        <v>7135699</v>
+        <v>7135758</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3074,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617252</v>
+        <v>129617346</v>
       </c>
       <c r="B24" t="n">
-        <v>92034</v>
+        <v>91551</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3171,48 +3171,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617346</v>
+        <v>129617736</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>98768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750816</v>
+        <v>750837</v>
       </c>
       <c r="R25" t="n">
-        <v>7135734</v>
+        <v>7135903</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3268,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617736</v>
+        <v>129617252</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>92040</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3279,41 +3283,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750837</v>
+        <v>750816</v>
       </c>
       <c r="R26" t="n">
-        <v>7135903</v>
+        <v>7135734</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129617837</v>
       </c>
       <c r="B27" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>129617841</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>129616725</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>129617917</v>
       </c>
       <c r="B30" t="n">
-        <v>95982</v>
+        <v>95994</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129618181</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129617065</v>
       </c>
       <c r="B32" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129617446</v>
       </c>
       <c r="B33" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97633</v>
+        <v>97645</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2767,7 +2767,7 @@
         <v>129617314</v>
       </c>
       <c r="B21" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>129616393</v>
       </c>
       <c r="B22" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>129617666</v>
       </c>
       <c r="B23" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>129617346</v>
       </c>
       <c r="B24" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>129617736</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>129617252</v>
       </c>
       <c r="B26" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129617837</v>
       </c>
       <c r="B27" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>129617841</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>129616725</v>
       </c>
       <c r="B29" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>129617917</v>
       </c>
       <c r="B30" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129618181</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129617065</v>
       </c>
       <c r="B32" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129617446</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97645</v>
+        <v>97646</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -3074,48 +3074,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617346</v>
+        <v>129617736</v>
       </c>
       <c r="B24" t="n">
-        <v>91552</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750816</v>
+        <v>750837</v>
       </c>
       <c r="R24" t="n">
-        <v>7135734</v>
+        <v>7135903</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3171,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617736</v>
+        <v>129617252</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>92041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,41 +3186,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750837</v>
+        <v>750816</v>
       </c>
       <c r="R25" t="n">
-        <v>7135903</v>
+        <v>7135734</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,32 +3272,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617252</v>
+        <v>129617346</v>
       </c>
       <c r="B26" t="n">
-        <v>92041</v>
+        <v>91552</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2880,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129616393</v>
+        <v>129617666</v>
       </c>
       <c r="B22" t="n">
-        <v>82911</v>
+        <v>91593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råkälen, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750947</v>
+        <v>750935</v>
       </c>
       <c r="R22" t="n">
-        <v>7135699</v>
+        <v>7135758</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129617666</v>
+        <v>129616393</v>
       </c>
       <c r="B23" t="n">
-        <v>91588</v>
+        <v>82916</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,34 +2988,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Råkälen, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750935</v>
+        <v>750947</v>
       </c>
       <c r="R23" t="n">
-        <v>7135758</v>
+        <v>7135699</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3074,52 +3074,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617736</v>
+        <v>129617346</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>91557</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750837</v>
+        <v>750816</v>
       </c>
       <c r="R24" t="n">
-        <v>7135903</v>
+        <v>7135734</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3178,7 +3174,7 @@
         <v>129617252</v>
       </c>
       <c r="B25" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,48 +3268,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617346</v>
+        <v>129617736</v>
       </c>
       <c r="B26" t="n">
-        <v>91552</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750816</v>
+        <v>750837</v>
       </c>
       <c r="R26" t="n">
-        <v>7135734</v>
+        <v>7135903</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129617837</v>
       </c>
       <c r="B27" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>129617841</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>129616725</v>
       </c>
       <c r="B29" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>129617917</v>
       </c>
       <c r="B30" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129618181</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129617065</v>
       </c>
       <c r="B32" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129617446</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97646</v>
+        <v>97651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -3074,48 +3074,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617346</v>
+        <v>129617736</v>
       </c>
       <c r="B24" t="n">
-        <v>91557</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750816</v>
+        <v>750837</v>
       </c>
       <c r="R24" t="n">
-        <v>7135734</v>
+        <v>7135903</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3268,52 +3272,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617736</v>
+        <v>129617346</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>91557</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750837</v>
+        <v>750816</v>
       </c>
       <c r="R26" t="n">
-        <v>7135903</v>
+        <v>7135734</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2880,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129617666</v>
+        <v>129616393</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
+        <v>82916</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Råkälen, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750935</v>
+        <v>750947</v>
       </c>
       <c r="R22" t="n">
-        <v>7135758</v>
+        <v>7135699</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129616393</v>
+        <v>129617666</v>
       </c>
       <c r="B23" t="n">
-        <v>82916</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,34 +2988,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råkälen, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750947</v>
+        <v>750935</v>
       </c>
       <c r="R23" t="n">
-        <v>7135699</v>
+        <v>7135758</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3074,52 +3074,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617736</v>
+        <v>129617346</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>91557</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750837</v>
+        <v>750816</v>
       </c>
       <c r="R24" t="n">
-        <v>7135903</v>
+        <v>7135734</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3175,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617252</v>
+        <v>129617736</v>
       </c>
       <c r="B25" t="n">
-        <v>92046</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,37 +3182,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750816</v>
+        <v>750837</v>
       </c>
       <c r="R25" t="n">
-        <v>7135734</v>
+        <v>7135903</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,32 +3272,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617346</v>
+        <v>129617252</v>
       </c>
       <c r="B26" t="n">
-        <v>91557</v>
+        <v>92046</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2880,10 +2880,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129616393</v>
+        <v>129617666</v>
       </c>
       <c r="B22" t="n">
-        <v>82916</v>
+        <v>91593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råkälen, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750947</v>
+        <v>750935</v>
       </c>
       <c r="R22" t="n">
-        <v>7135699</v>
+        <v>7135758</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129617666</v>
+        <v>129616393</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>82916</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2988,34 +2988,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Råkälen, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750935</v>
+        <v>750947</v>
       </c>
       <c r="R23" t="n">
-        <v>7135758</v>
+        <v>7135699</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3074,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617346</v>
+        <v>129617252</v>
       </c>
       <c r="B24" t="n">
-        <v>91557</v>
+        <v>92046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3171,52 +3171,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617736</v>
+        <v>129617346</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>91557</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750837</v>
+        <v>750816</v>
       </c>
       <c r="R25" t="n">
-        <v>7135903</v>
+        <v>7135734</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,10 +3268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617252</v>
+        <v>129617736</v>
       </c>
       <c r="B26" t="n">
-        <v>92046</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,37 +3279,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750816</v>
+        <v>750837</v>
       </c>
       <c r="R26" t="n">
-        <v>7135734</v>
+        <v>7135903</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2883,7 +2883,7 @@
         <v>129617666</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3074,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617252</v>
+        <v>129617346</v>
       </c>
       <c r="B24" t="n">
-        <v>92046</v>
+        <v>91561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617346</v>
+        <v>129617252</v>
       </c>
       <c r="B25" t="n">
-        <v>91557</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
         <v>129617736</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>129616725</v>
       </c>
       <c r="B29" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>129617917</v>
       </c>
       <c r="B30" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129618181</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129617065</v>
       </c>
       <c r="B32" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129617446</v>
+        <v>129617473</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4079,7 +4079,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97651</v>
+        <v>97655</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2883,7 +2883,7 @@
         <v>129617666</v>
       </c>
       <c r="B22" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>129616393</v>
       </c>
       <c r="B23" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>129617346</v>
       </c>
       <c r="B24" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617252</v>
+        <v>129617736</v>
       </c>
       <c r="B25" t="n">
-        <v>92050</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3182,37 +3182,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750816</v>
+        <v>750837</v>
       </c>
       <c r="R25" t="n">
-        <v>7135734</v>
+        <v>7135903</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3268,10 +3272,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617736</v>
+        <v>129617252</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>92052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3279,41 +3283,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750837</v>
+        <v>750816</v>
       </c>
       <c r="R26" t="n">
-        <v>7135903</v>
+        <v>7135734</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>129616725</v>
       </c>
       <c r="B29" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>129617917</v>
       </c>
       <c r="B30" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129618181</v>
       </c>
       <c r="B31" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129617065</v>
       </c>
       <c r="B32" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129617473</v>
+        <v>129617446</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4079,7 +4079,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97655</v>
+        <v>97657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -3074,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617346</v>
+        <v>129617252</v>
       </c>
       <c r="B24" t="n">
-        <v>91563</v>
+        <v>92052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3171,52 +3171,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617736</v>
+        <v>129617346</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>91563</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750837</v>
+        <v>750816</v>
       </c>
       <c r="R25" t="n">
-        <v>7135903</v>
+        <v>7135734</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3272,10 +3268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617252</v>
+        <v>129617736</v>
       </c>
       <c r="B26" t="n">
-        <v>92052</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,37 +3279,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750816</v>
+        <v>750837</v>
       </c>
       <c r="R26" t="n">
-        <v>7135734</v>
+        <v>7135903</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -3271,7 +3271,7 @@
         <v>129617736</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>129617917</v>
       </c>
       <c r="B30" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129618181</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129617446</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97657</v>
+        <v>97667</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -3074,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617252</v>
+        <v>129617346</v>
       </c>
       <c r="B24" t="n">
-        <v>92052</v>
+        <v>91563</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617346</v>
+        <v>129617252</v>
       </c>
       <c r="B25" t="n">
-        <v>91563</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -3074,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617346</v>
+        <v>129617252</v>
       </c>
       <c r="B24" t="n">
-        <v>91563</v>
+        <v>92052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617252</v>
+        <v>129617346</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>91563</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2767,7 +2767,7 @@
         <v>129617314</v>
       </c>
       <c r="B21" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>129617666</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>129616393</v>
       </c>
       <c r="B23" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617252</v>
+        <v>129617346</v>
       </c>
       <c r="B24" t="n">
-        <v>92052</v>
+        <v>91566</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617346</v>
+        <v>129617252</v>
       </c>
       <c r="B25" t="n">
-        <v>91563</v>
+        <v>92055</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
         <v>129617736</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129617837</v>
       </c>
       <c r="B27" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>129617841</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>129616725</v>
       </c>
       <c r="B29" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>129617917</v>
       </c>
       <c r="B30" t="n">
-        <v>96016</v>
+        <v>96020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129618181</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129617065</v>
       </c>
       <c r="B32" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129617446</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -2767,7 +2767,7 @@
         <v>129617314</v>
       </c>
       <c r="B21" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>129617666</v>
       </c>
       <c r="B22" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>129616393</v>
       </c>
       <c r="B23" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3074,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617346</v>
+        <v>129617252</v>
       </c>
       <c r="B24" t="n">
-        <v>91566</v>
+        <v>92058</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3171,32 +3171,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617252</v>
+        <v>129617346</v>
       </c>
       <c r="B25" t="n">
-        <v>92055</v>
+        <v>91569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
         <v>129617736</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>129617837</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79119</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>129617841</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>129616725</v>
       </c>
       <c r="B29" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>129617917</v>
       </c>
       <c r="B30" t="n">
-        <v>96020</v>
+        <v>96023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>129618181</v>
       </c>
       <c r="B31" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>129617065</v>
       </c>
       <c r="B32" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>129617446</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4185,6 +4185,103 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130888653</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Botsmarksblocket, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>751036</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7136039</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104865032</v>
+        <v>104865034</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750867.2130251171</v>
+        <v>750814</v>
       </c>
       <c r="R2" t="n">
-        <v>7135825.934375396</v>
+        <v>7135930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104865035</v>
+        <v>129617837</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råkälen, Botsmark, Umeå, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750808.5990430546</v>
+        <v>750835</v>
       </c>
       <c r="R3" t="n">
-        <v>7135928.108939235</v>
+        <v>7135953</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,69 +861,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104865037</v>
+        <v>129616547</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råkälen, Botsmark, Umeå, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750789.5749295906</v>
+        <v>750935</v>
       </c>
       <c r="R4" t="n">
-        <v>7135850.59182239</v>
+        <v>7135758</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,50 +954,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104865031</v>
+        <v>129617252</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,34 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råkälen, Botsmark, Umeå, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750905.5256189171</v>
+        <v>750816</v>
       </c>
       <c r="R5" t="n">
-        <v>7135699.395328169</v>
+        <v>7135734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,22 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,69 +1055,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104865033</v>
+        <v>129616393</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Råkälen, Botsmark, Umeå, Vb</t>
+          <t>Råkälen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750837.6923152391</v>
+        <v>750947</v>
       </c>
       <c r="R6" t="n">
-        <v>7135930.484695835</v>
+        <v>7135699</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,22 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,69 +1152,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104865034</v>
+        <v>129617917</v>
       </c>
       <c r="B7" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råkälen, Botsmark, Umeå, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750813.6681288374</v>
+        <v>750880</v>
       </c>
       <c r="R7" t="n">
-        <v>7135930.269133787</v>
+        <v>7136021</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,22 +1229,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,71 +1249,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104865036</v>
+        <v>104865037</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Råkälen, Botsmark, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750794.5994265587</v>
+        <v>750790</v>
       </c>
       <c r="R8" t="n">
-        <v>7135847.946006809</v>
+        <v>7135851</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,21 +1329,11 @@
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1487,6 +1342,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1507,65 +1377,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111298554</v>
+        <v>129616725</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Råkälen, Botsmark, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750810.9216889167</v>
+        <v>750869</v>
       </c>
       <c r="R9" t="n">
-        <v>7135830.06918097</v>
+        <v>7135674</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,22 +1442,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,76 +1456,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Henrik Sporrong</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Henrik Sporrong</t>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121659103</v>
+        <v>129617065</v>
       </c>
       <c r="B10" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högliden, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750865</v>
+        <v>750824</v>
       </c>
       <c r="R10" t="n">
-        <v>7135826</v>
+        <v>7135678</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,12 +1539,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,65 +1559,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121659101</v>
+        <v>129617231</v>
       </c>
       <c r="B11" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högliden, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750896</v>
+        <v>750816</v>
       </c>
       <c r="R11" t="n">
-        <v>7136026</v>
+        <v>7135734</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,12 +1636,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,38 +1650,32 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121659096</v>
+        <v>104865031</v>
       </c>
       <c r="B12" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1878,19 +1697,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Högliden, Vb</t>
+          <t>Råkälen, Botsmark, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750985</v>
+        <v>750905</v>
       </c>
       <c r="R12" t="n">
-        <v>7136054</v>
+        <v>7135699</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,12 +1733,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,29 +1747,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125232522</v>
+        <v>104865032</v>
       </c>
       <c r="B13" t="n">
-        <v>98331</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1961,38 +1780,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Högliden, Vb</t>
+          <t>Råkälen, Botsmark, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750844</v>
+        <v>750867</v>
       </c>
       <c r="R13" t="n">
-        <v>7136020</v>
+        <v>7135826</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,12 +1834,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,29 +1848,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125232631</v>
+        <v>104865035</v>
       </c>
       <c r="B14" t="n">
-        <v>98331</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2063,38 +1881,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Högliden, Vb</t>
+          <t>Råkälen, Botsmark, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750805</v>
+        <v>750809</v>
       </c>
       <c r="R14" t="n">
-        <v>7135996</v>
+        <v>7135928</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,12 +1935,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,29 +1949,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125232436</v>
+        <v>121659096</v>
       </c>
       <c r="B15" t="n">
-        <v>98331</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,27 +1982,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2193,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750987</v>
+        <v>750985</v>
       </c>
       <c r="R15" t="n">
-        <v>7136030</v>
+        <v>7136054</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,12 +2039,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2072,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125232490</v>
+        <v>121659101</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,27 +2083,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2295,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750909</v>
+        <v>750896</v>
       </c>
       <c r="R16" t="n">
-        <v>7136045</v>
+        <v>7136026</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,12 +2140,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,10 +2173,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125232601</v>
+        <v>125382120</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,38 +2184,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Högliden, Vb</t>
+          <t>Västermark, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750822</v>
+        <v>751035</v>
       </c>
       <c r="R17" t="n">
-        <v>7135979</v>
+        <v>7136038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,75 +2252,66 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125232702</v>
+        <v>129617841</v>
       </c>
       <c r="B18" t="n">
-        <v>56843</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Högliden, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>750862</v>
+        <v>750835</v>
       </c>
       <c r="R18" t="n">
-        <v>7135880</v>
+        <v>7135953</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,12 +2335,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2553,64 +2355,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>David Magnusson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>David Magnusson, Manne Frih, David Kenger</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125232751</v>
+        <v>130888653</v>
       </c>
       <c r="B19" t="n">
-        <v>97209</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Högliden, Vb</t>
+          <t>Botsmarksblocket, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750869</v>
+        <v>751036</v>
       </c>
       <c r="R19" t="n">
-        <v>7135811</v>
+        <v>7136039</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2648,64 +2446,68 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125382120</v>
+        <v>104865036</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västermark, Vb</t>
+          <t>Råkälen, Botsmark, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751035</v>
+        <v>750795</v>
       </c>
       <c r="R20" t="n">
-        <v>7136038</v>
+        <v>7135848</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,12 +2534,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2752,39 +2554,43 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129617314</v>
+        <v>121659103</v>
       </c>
       <c r="B21" t="n">
-        <v>56921</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2792,36 +2598,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Högliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>750816</v>
+        <v>750865</v>
       </c>
       <c r="R21" t="n">
-        <v>7135734</v>
+        <v>7135826</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,12 +2639,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,60 +2659,68 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129617666</v>
+        <v>125232702</v>
       </c>
       <c r="B22" t="n">
-        <v>91605</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Högliden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>750935</v>
+        <v>750862</v>
       </c>
       <c r="R22" t="n">
-        <v>7135758</v>
+        <v>7135880</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2945,12 +2744,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2965,60 +2764,79 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129616393</v>
+        <v>129617314</v>
       </c>
       <c r="B23" t="n">
-        <v>82924</v>
+        <v>57132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Råkälen, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>750947</v>
+        <v>750816</v>
       </c>
       <c r="R23" t="n">
-        <v>7135699</v>
+        <v>7135734</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3074,10 +2892,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129617252</v>
+        <v>104865033</v>
       </c>
       <c r="B24" t="n">
-        <v>92058</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3085,34 +2903,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Råkälen, Botsmark, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>750816</v>
+        <v>750838</v>
       </c>
       <c r="R24" t="n">
-        <v>7135734</v>
+        <v>7135930</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,12 +2957,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,60 +2977,76 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129617346</v>
+        <v>111298554</v>
       </c>
       <c r="B25" t="n">
-        <v>91569</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Råkälen, Botsmark, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>750816</v>
+        <v>750811</v>
       </c>
       <c r="R25" t="n">
-        <v>7135734</v>
+        <v>7135831</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3236,12 +3070,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3250,28 +3084,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Henrik Sporrong</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
+          <t>Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129617736</v>
+        <v>125232436</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3296,24 +3131,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Högliden, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>750837</v>
+        <v>750987</v>
       </c>
       <c r="R26" t="n">
-        <v>7135903</v>
+        <v>7136030</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3337,12 +3172,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3351,66 +3186,71 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129617837</v>
+        <v>125232490</v>
       </c>
       <c r="B27" t="n">
-        <v>79119</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Högliden, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>750835</v>
+        <v>750909</v>
       </c>
       <c r="R27" t="n">
-        <v>7135953</v>
+        <v>7136045</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3434,12 +3274,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3448,66 +3288,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129617841</v>
+        <v>125232522</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Högliden, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>750835</v>
+        <v>750844</v>
       </c>
       <c r="R28" t="n">
-        <v>7135953</v>
+        <v>7136020</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3531,12 +3376,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3545,66 +3390,71 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129616725</v>
+        <v>125232601</v>
       </c>
       <c r="B29" t="n">
-        <v>91569</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Högliden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>750869</v>
+        <v>750822</v>
       </c>
       <c r="R29" t="n">
-        <v>7135674</v>
+        <v>7135979</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3628,12 +3478,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,66 +3492,71 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129617917</v>
+        <v>125232631</v>
       </c>
       <c r="B30" t="n">
-        <v>96023</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Högliden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>750880</v>
+        <v>750805</v>
       </c>
       <c r="R30" t="n">
-        <v>7136021</v>
+        <v>7135996</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3725,12 +3580,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3739,28 +3594,29 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>David Magnusson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>David Magnusson, Manne Frih, David Kenger</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129618181</v>
+        <v>129617446</v>
       </c>
       <c r="B31" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3787,7 +3643,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3802,14 +3658,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lasskläppen, Lasskläppen, Vb</t>
+          <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751041</v>
+        <v>750828</v>
       </c>
       <c r="R31" t="n">
-        <v>7136032</v>
+        <v>7135831</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3868,45 +3724,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129617065</v>
+        <v>129617685</v>
       </c>
       <c r="B32" t="n">
-        <v>91569</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Råkälens NV-sida vid väg 620, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>750824</v>
+        <v>750837</v>
       </c>
       <c r="R32" t="n">
-        <v>7135678</v>
+        <v>7135903</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3965,10 +3835,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129617446</v>
+        <v>129618181</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,7 +3865,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4010,14 +3880,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Råkälens NV-sida vid väg 620, Vb</t>
+          <t>Lasskläppen, Lasskläppen, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>750828</v>
+        <v>751041</v>
       </c>
       <c r="R33" t="n">
-        <v>7135831</v>
+        <v>7136032</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4079,7 +3949,7 @@
         <v>129617696</v>
       </c>
       <c r="B34" t="n">
-        <v>97674</v>
+        <v>97989</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4187,48 +4057,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130888653</v>
+        <v>125232751</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>97983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Botsmarksblocket, Vb</t>
+          <t>Högliden, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>751036</v>
+        <v>750869</v>
       </c>
       <c r="R35" t="n">
-        <v>7136039</v>
+        <v>7135811</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4266,18 +4140,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 22575-2024 artfynd.xlsx
+++ b/artfynd/A 22575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104865034</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617837</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616547</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617252</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616393</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617917</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104865037</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616725</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1568,6 +1613,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617065</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617231</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104865031</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1867,6 +1927,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104865032</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1966,6 +2031,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104865035</t>
         </is>
       </c>
     </row>
@@ -2069,6 +2139,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121659096</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2170,6 +2245,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121659101</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2267,6 +2347,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125382120</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2364,6 +2449,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617841</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2461,6 +2551,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130888653</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104865036</t>
         </is>
       </c>
     </row>
@@ -2668,6 +2768,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121659103</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2773,6 +2878,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125232702</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2889,6 +2999,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617314</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2990,6 +3105,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104865033</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3100,6 +3220,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111298554</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3202,6 +3327,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125232436</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3304,6 +3434,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125232490</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3406,6 +3541,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125232522</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3508,6 +3648,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125232601</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3610,6 +3755,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125232631</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3721,6 +3871,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617446</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3832,6 +3987,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617685</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3943,6 +4103,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129618181</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4054,6 +4219,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617696</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4156,8 +4326,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125232751</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>